--- a/Result/profitability/9925.xlsx
+++ b/Result/profitability/9925.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="N2" t="n">
-        <v>34.17375</v>
+        <v>33.73625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>0.51625</v>
+        <v>0.6437499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>34.69374999999999</v>
+        <v>34.21875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.49</v>
+        <v>0.61875</v>
       </c>
       <c r="N4" t="n">
-        <v>35.36499999999999</v>
+        <v>35.12125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5237499999999999</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>35.65875</v>
+        <v>35.595</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,13 +1137,13 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.47625</v>
+        <v>0.5637500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>35.9475</v>
+        <v>35.66875</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.98</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5037499999999999</v>
+        <v>0.645</v>
       </c>
       <c r="N7" t="n">
-        <v>35.83875</v>
+        <v>35.76375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5249999999999999</v>
+        <v>0.6487499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>36.77625</v>
+        <v>36.63625</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0.57</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5512499999999999</v>
+        <v>0.55125</v>
       </c>
       <c r="N13" t="n">
         <v>36.89749999999999</v>
@@ -9335,13 +9335,13 @@
         <v>2008</v>
       </c>
       <c r="D71" t="n">
-        <v>1302</v>
+        <v>1375</v>
       </c>
       <c r="E71" t="n">
-        <v>706</v>
+        <v>633</v>
       </c>
       <c r="F71" t="n">
-        <v>35.18</v>
+        <v>31.5</v>
       </c>
       <c r="G71" t="n">
         <v>192</v>
@@ -9367,7 +9367,7 @@
         <v>0.56875</v>
       </c>
       <c r="N71" t="n">
-        <v>34.58125</v>
+        <v>34.12125</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -9379,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -9400,10 +9400,10 @@
         <v>0.9767441860465116</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.240000000000002</v>
+        <v>-1.439999999999998</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.06800242865816641</v>
+        <v>-0.04371584699453546</v>
       </c>
       <c r="AA71" t="n">
         <v>-0.04000000000000004</v>
@@ -9412,10 +9412,10 @@
         <v>-0.0449438202247191</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.3800000000000026</v>
+        <v>-3.299999999999997</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.01091954022988517</v>
+        <v>-0.09482758620689646</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -9424,17 +9424,17 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率成長</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -9462,13 +9462,13 @@
         <v>2036</v>
       </c>
       <c r="D72" t="n">
-        <v>1358</v>
+        <v>1285</v>
       </c>
       <c r="E72" t="n">
-        <v>677</v>
+        <v>751</v>
       </c>
       <c r="F72" t="n">
-        <v>33.28</v>
+        <v>36.9</v>
       </c>
       <c r="G72" t="n">
         <v>178</v>
@@ -9494,7 +9494,7 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>34.4025</v>
+        <v>34.395</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -9506,7 +9506,7 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -9527,10 +9527,10 @@
         <v>-0.1058823529411764</v>
       </c>
       <c r="Y72" t="n">
-        <v>-1.899999999999999</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="Z72" t="n">
-        <v>-0.05400795906765199</v>
+        <v>0.1714285714285715</v>
       </c>
       <c r="AA72" t="n">
         <v>0.3</v>
@@ -9539,10 +9539,10 @@
         <v>0.6521739130434783</v>
       </c>
       <c r="AC72" t="n">
-        <v>-1.210000000000001</v>
+        <v>2.409999999999997</v>
       </c>
       <c r="AD72" t="n">
-        <v>-0.03508263264714417</v>
+        <v>0.06987532618150172</v>
       </c>
       <c r="AE72" t="n">
         <v>0</v>
@@ -9551,17 +9551,17 @@
         <v>1</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率衰退</t>
+          <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
       <c r="AK72" t="n">
@@ -9621,7 +9621,7 @@
         <v>0.585</v>
       </c>
       <c r="N73" t="n">
-        <v>33.99125</v>
+        <v>33.98375</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9654,10 +9654,10 @@
         <v>-0.5657894736842105</v>
       </c>
       <c r="Y73" t="n">
-        <v>-1.630000000000003</v>
+        <v>-5.25</v>
       </c>
       <c r="Z73" t="n">
-        <v>-0.04897836538461542</v>
+        <v>-0.1422764227642277</v>
       </c>
       <c r="AA73" t="n">
         <v>-0.11</v>
@@ -9748,7 +9748,7 @@
         <v>0.5787500000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>33.6625</v>
+        <v>33.655</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9925</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2064</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1423</v>
+      </c>
+      <c r="E75" t="n">
+        <v>641</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>184</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.93%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>493</v>
+      </c>
+      <c r="J75" t="n">
+        <v>677</v>
+      </c>
+      <c r="K75" t="n">
+        <v>563</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.18625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.106382978723405</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.120000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03481504507304944</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7176470588235293</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4499999999999993</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01428571428571423</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
